--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-task-moyen-ressource.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-task-moyen-ressource.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T14:23:39+00:00</t>
+    <t>2026-01-28T15:00:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-task-moyen-ressource.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-task-moyen-ressource.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T15:00:38+00:00</t>
+    <t>2026-01-28T15:51:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1586,7 +1586,7 @@
     <t>Inputs are named to enable task automation to bind data and pass it from one task to the next.</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/input-tddui-task-moyen-ressource-valueset|2.2.0-ballot</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/input-tddui-task-moyen-ressource|2.2.0-ballot</t>
   </si>
   <si>
     <t>Task.input.value[x]</t>
@@ -1628,7 +1628,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-moyen-ressource-codesystem"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-moyen-ressource"/&gt;
     &lt;code value="titre"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1663,7 +1663,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-moyen-ressource-codesystem"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-moyen-ressource"/&gt;
     &lt;code value="evaluation"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1702,7 +1702,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-moyen-ressource-codesystem"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-moyen-ressource"/&gt;
     &lt;code value="pieceJointe"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -2090,7 +2090,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="143.0390625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="85.34765625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="78.0859375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-task-moyen-ressource.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-task-moyen-ressource.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T15:51:30+00:00</t>
+    <t>2026-02-02T09:49:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1586,7 +1586,7 @@
     <t>Inputs are named to enable task automation to bind data and pass it from one task to the next.</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/input-tddui-task-moyen-ressource|2.2.0-ballot</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-task-input-moyen-ressource|2.2.0-ballot</t>
   </si>
   <si>
     <t>Task.input.value[x]</t>
@@ -1628,7 +1628,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-moyen-ressource"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-task-input-moyen-ressource"/&gt;
     &lt;code value="titre"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1663,7 +1663,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-moyen-ressource"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-task-input-moyen-ressource"/&gt;
     &lt;code value="evaluation"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1702,7 +1702,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-moyen-ressource"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-task-input-moyen-ressource"/&gt;
     &lt;code value="pieceJointe"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>

--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-task-moyen-ressource.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-task-moyen-ressource.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T09:49:54+00:00</t>
+    <t>2026-02-02T14:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-task-moyen-ressource.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-task-moyen-ressource.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T14:44:55+00:00</t>
+    <t>2026-02-04T16:15:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-task-moyen-ressource.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-task-moyen-ressource.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T16:15:13+00:00</t>
+    <t>2026-02-05T08:25:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
